--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -14,17 +14,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -43,12 +37,6 @@
     <t>位置</t>
   </si>
   <si>
-    <t>身高</t>
-  </si>
-  <si>
-    <t>体重</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -58,12 +46,6 @@
     <t>Position</t>
   </si>
   <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -97,15 +79,134 @@
     <t>带有强力攻击技能4</t>
   </si>
   <si>
-    <t>测试</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsTest</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
+    <t>#</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄小雨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>郭晓华</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>西纱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑士</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>法师</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>盗贼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧师</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓箭手</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Str</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LUK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intell</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agi</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aoi</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>JobHp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>JobSp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度*1000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量Job系数*1000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝量Job系数*1000</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -113,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +226,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -132,11 +234,21 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -167,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -177,6 +289,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -478,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:K9"/>
+  <dimension ref="B1:R14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -488,110 +601,174 @@
     <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="7.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.875" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="18.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9" style="2"/>
+    <col min="11" max="12" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:18" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="s">
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I3" s="3" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -599,28 +776,52 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>68</v>
-      </c>
-      <c r="K6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -628,30 +829,51 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H7" s="1">
         <v>2</v>
       </c>
       <c r="I7" s="1">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>78</v>
-      </c>
-      <c r="K7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1">
         <v>1003</v>
@@ -660,30 +882,51 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="1">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>68</v>
-      </c>
-      <c r="K8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1">
         <v>1004</v>
@@ -692,24 +935,295 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>78</v>
-      </c>
-      <c r="K9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C10" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J10" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K10" s="1">
+        <v>700</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C11" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J11" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K11" s="1">
+        <v>300</v>
+      </c>
+      <c r="L11" s="1">
+        <v>6000</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>1</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C12" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K12" s="1">
+        <v>500</v>
+      </c>
+      <c r="L12" s="1">
+        <v>3000</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C13" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4</v>
+      </c>
+      <c r="I13" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J13" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K13" s="1">
+        <v>400</v>
+      </c>
+      <c r="L13" s="1">
+        <v>4000</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C14" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5</v>
+      </c>
+      <c r="I14" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J14" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K14" s="1">
+        <v>500</v>
+      </c>
+      <c r="L14" s="1">
+        <v>3000</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>1</v>
+      </c>
+      <c r="R14" s="1">
         <v>1</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -207,6 +207,14 @@
   </si>
   <si>
     <t>蓝量Job系数*1000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹所有Unit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -591,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R14"/>
+  <dimension ref="B1:R15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1227,6 +1235,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C15" s="1">
+        <v>9001</v>
+      </c>
+      <c r="D15" s="1">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -215,6 +215,22 @@
   </si>
   <si>
     <t>子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物测试1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物测试2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R15"/>
+  <dimension ref="B1:R17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1285,6 +1301,106 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C16" s="1">
+        <v>10001</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C17" s="1">
+        <v>10002</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBE09CA-AAE6-460E-82C6-6D7E08AA2188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13065"/>
+    <workbookView xWindow="0" yWindow="2400" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -237,7 +243,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -324,14 +330,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -369,7 +378,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -441,7 +450,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -614,7 +623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:R17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBE09CA-AAE6-460E-82C6-6D7E08AA2188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16582908-DC60-4D1D-8B57-99C570C3AAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2400" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2055" yWindow="2430" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -237,6 +237,14 @@
   </si>
   <si>
     <t>怪物2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否远程（玩家伤害计算用）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -624,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:R17"/>
+  <dimension ref="B1:S17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -637,14 +645,16 @@
     <col min="9" max="9" width="18.5" style="2" customWidth="1"/>
     <col min="10" max="10" width="9" style="2"/>
     <col min="11" max="12" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="13" max="13" width="22.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:19" ht="15.75" x14ac:dyDescent="0.3">
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="M1" s="5"/>
+    </row>
+    <row r="2" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
@@ -652,7 +662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -684,25 +694,28 @@
         <v>53</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -732,25 +745,28 @@
         <v>47</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
@@ -797,8 +813,11 @@
       <c r="R5" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="S5" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
@@ -833,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
@@ -850,8 +869,11 @@
       <c r="R6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
@@ -886,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="1">
         <v>0</v>
@@ -903,8 +925,11 @@
       <c r="R7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
@@ -939,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="1">
         <v>0</v>
@@ -956,8 +981,11 @@
       <c r="R8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
@@ -992,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="1">
         <v>0</v>
@@ -1009,8 +1037,11 @@
       <c r="R9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>1001</v>
       </c>
@@ -1059,8 +1090,11 @@
       <c r="R10" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="S10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C11" s="1">
         <v>1002</v>
       </c>
@@ -1109,8 +1143,11 @@
       <c r="R11" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="S11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C12" s="1">
         <v>1003</v>
       </c>
@@ -1159,8 +1196,11 @@
       <c r="R12" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="S12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C13" s="1">
         <v>1004</v>
       </c>
@@ -1209,8 +1249,11 @@
       <c r="R13" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="S13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C14" s="1">
         <v>1005</v>
       </c>
@@ -1242,7 +1285,7 @@
         <v>3000</v>
       </c>
       <c r="M14" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N14" s="1">
         <v>1</v>
@@ -1259,8 +1302,11 @@
       <c r="R14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="S14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C15" s="1">
         <v>9001</v>
       </c>
@@ -1292,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1">
         <v>0</v>
@@ -1309,8 +1355,11 @@
       <c r="R15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C16" s="1">
         <v>10001</v>
       </c>
@@ -1333,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -1342,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="1">
         <v>0</v>
@@ -1357,10 +1406,13 @@
         <v>0</v>
       </c>
       <c r="R16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="S16" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C17" s="1">
         <v>10002</v>
       </c>
@@ -1383,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -1392,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="1">
         <v>0</v>
@@ -1407,7 +1459,10 @@
         <v>0</v>
       </c>
       <c r="R17" s="1">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="S17" s="1">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -1,26 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16582908-DC60-4D1D-8B57-99C570C3AAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="2430" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23520" windowHeight="11670"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
   <si>
     <t>#</t>
   </si>
@@ -43,6 +55,39 @@
     <t>位置</t>
   </si>
   <si>
+    <t>速度*1000</t>
+  </si>
+  <si>
+    <t>AOI</t>
+  </si>
+  <si>
+    <t>血量Job系数*1000</t>
+  </si>
+  <si>
+    <t>蓝量Job系数*1000</t>
+  </si>
+  <si>
+    <t>是否远程（玩家伤害计算用）</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>AGI</t>
+  </si>
+  <si>
+    <t>VIT</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>DEX</t>
+  </si>
+  <si>
+    <t>LUK</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -52,12 +97,48 @@
     <t>Position</t>
   </si>
   <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Aoi</t>
+  </si>
+  <si>
+    <t>JobHp</t>
+  </si>
+  <si>
+    <t>JobSp</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Str</t>
+  </si>
+  <si>
+    <t>Agi</t>
+  </si>
+  <si>
+    <t>Vit</t>
+  </si>
+  <si>
+    <t>Intell</t>
+  </si>
+  <si>
+    <t>Dex</t>
+  </si>
+  <si>
+    <t>Luk</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>米克尔</t>
   </si>
   <si>
@@ -85,174 +166,59 @@
     <t>带有强力攻击技能4</t>
   </si>
   <si>
-    <t>#</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄小雨</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>角色数值模板</t>
+  </si>
+  <si>
+    <t>通用模板</t>
   </si>
   <si>
     <t>郭晓华</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>法师</t>
   </si>
   <si>
     <t>西纱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Speed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>剑士</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>法师</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>盗贼</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>牧师</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>弓箭手</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Str</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGI</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>STR</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIT</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LUK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Luk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dex</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Intell</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Agi</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOI</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Aoi</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>JobHp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>JobSp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>速度*1000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量Job系数*1000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝量Job系数*1000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>子弹所有Unit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>子弹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>怪物测试1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>怪物1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>怪物测试2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>怪物2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否远程（玩家伤害计算用）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Range</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,34 +230,168 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,8 +404,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -313,9 +599,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -323,23 +851,67 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -626,14 +1198,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B1:S17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
@@ -644,17 +1216,17 @@
     <col min="8" max="8" width="7.875" style="2" customWidth="1"/>
     <col min="9" max="9" width="18.5" style="2" customWidth="1"/>
     <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="12" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="15" style="2" customWidth="1"/>
+    <col min="13" max="13" width="22.25" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+    <row r="1" spans="2:19">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
     </row>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:19">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
@@ -662,164 +1234,164 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="3" spans="2:19">
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N3" s="3" t="s">
+      <c r="I3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19">
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19">
+      <c r="C5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>38</v>
+      <c r="M5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" s="1" customFormat="1" spans="2:19">
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1">
         <v>1001</v>
@@ -831,10 +1403,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -873,9 +1445,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="7" s="1" customFormat="1" spans="2:19">
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1">
         <v>1002</v>
@@ -884,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="H7" s="1">
         <v>2</v>
@@ -929,9 +1501,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" s="1" customFormat="1" spans="2:19">
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1">
         <v>1003</v>
@@ -943,10 +1515,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -985,9 +1557,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="9" s="1" customFormat="1" spans="2:19">
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C9" s="1">
         <v>1004</v>
@@ -996,13 +1568,13 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>20</v>
+        <v>42</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
@@ -1041,7 +1613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:19">
       <c r="C10" s="1">
         <v>1001</v>
       </c>
@@ -1049,13 +1621,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
@@ -1094,7 +1666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:19">
       <c r="C11" s="1">
         <v>1002</v>
       </c>
@@ -1102,13 +1674,13 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -1147,7 +1719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:19">
       <c r="C12" s="1">
         <v>1003</v>
       </c>
@@ -1155,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H12" s="1">
         <v>3</v>
@@ -1200,7 +1772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:19">
       <c r="C13" s="1">
         <v>1004</v>
       </c>
@@ -1208,13 +1780,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H13" s="1">
         <v>4</v>
@@ -1253,7 +1825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:19">
       <c r="C14" s="1">
         <v>1005</v>
       </c>
@@ -1261,13 +1833,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="H14" s="1">
         <v>5</v>
@@ -1306,7 +1878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:19">
       <c r="C15" s="1">
         <v>9001</v>
       </c>
@@ -1314,13 +1886,13 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -1359,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:19">
       <c r="C16" s="1">
         <v>10001</v>
       </c>
@@ -1367,13 +1939,13 @@
         <v>2</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -1412,7 +1984,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:19">
       <c r="C17" s="1">
         <v>10002</v>
       </c>
@@ -1420,13 +1992,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1466,8 +2038,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>